--- a/bin/Debug/net472/scripts/test_results.xlsx
+++ b/bin/Debug/net472/scripts/test_results.xlsx
@@ -7,8 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="web__availability" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="web__navigation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="snmp__check" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ssh__UsIn__user__management" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="web__navigation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ssh__UsIn__vlan__name__full" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ssh__sntp__config" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,10 +71,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -432,15 +442,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,22 +488,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:29</t>
+          <t>2026-05-05 16:15:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>web__availability</t>
+          <t>snmp__check</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Открыть web-интерфейс</t>
+          <t>GET 1.3.6.1.2.1.1.3.0 (Аптайм (sysUpTime))</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -503,7 +513,679 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Страница загружена. Статус: 200</t>
+          <t>1654499</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:46</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.1 (Link Порт 1 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.2 (Link Порт 2 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:46</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.3 (Link Порт 3 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:46</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.4 (Link Порт 4 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:47</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.5 (Link Порт 5 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:47</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.6 (Link Порт 6 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:47</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.7 (Link Порт 7 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:47</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.8 (Link Порт 8 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:47</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.2.1.2.2.1.8.9 (Link Порт 9 (1=Up, 2=Down))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:48</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.1 (PoE Порт 1)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:48</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.2 (PoE Порт 2)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.3 (PoE Порт 3)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:49</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.4 (PoE Порт 4)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:49</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.5 (PoE Порт 5)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.6 (PoE Порт 6)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:50</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.7 (PoE Порт 7)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:51</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.2.8 (PoE Порт 8)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:51</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.5.1.1.3.2 (Что-то2)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:51</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2 (Status PSW)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ошибка SNMP: noSuchName</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:52</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.1 (UPS status)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ошибка SNMP: noSuchName</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:52</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>snmp__check</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GET 1.3.6.1.4.1.42019.3.2.2.2 (Input status)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ошибка SNMP: noSuchName</t>
         </is>
       </c>
     </row>
@@ -513,6 +1195,571 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ожидаемое значение</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:46</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t># Автотест начат</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:46</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>#1. Создание пользователей (под admin)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:48</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>system user config add user_name test_full password 111 admin_rule full</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>test_full</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>info: user test_full add successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:51</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>system user config add user_name test_user password 222 admin_rule read_only</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>test_user</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>info: user test_user add successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:53</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t># Подключение под test_full (Должно быть Успех)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:55</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>system user show configuration</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>show</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>..............................................
+Useer name:    test_full
+	Read access:     full access
+	Write access:    full access
+..............................................
+Useer name:    admin
+	Read access:     full access
+	Write access:    full access
+..............................................
+Useer name:    test_user
+	Read access:     full access
+	Write access:    denied</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:56</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>system user config add user_name test_add_admin password 333 admin_rule read_only</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>info: user test_add_admin add successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:15:58</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t># Подключение под test_user (show должен отрабоать)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>system user show configuration</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>show</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>..............................................
+Useer name:    test_add_admin
+	Read access:     full access
+	Write access:    denied
+..............................................
+Useer name:    test_full
+	Read access:     full access
+	Write access:    full access
+..............................................
+Useer name:    admin
+	Read access:     full access
+	Write access:    full access
+..............................................
+Useer name:    test_user
+	Read access:     full access
+	Write access:    denied</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t># Подключение под test_user (config должен выдать Ошибку)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>system user config add user_name test_add_user password 444 admin_rule read_only</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Syntax error: Illegal command line
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>#2. Очистка системы (Снова под admin)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>system user config delete user_name test_full</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>test_full</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>info: user test_full delete successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:08</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>system user config delete user_name test_user</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>test_user</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>info: user test_user delete successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>system user config add user_name test_add_admin password 333 admin_rule read_only</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>error: User *test_add_admin* is present</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__user__management</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t># Автотест завершён</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -526,6 +1773,988 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ожидаемое значение</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Сбор ссылок меню</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Список собран</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Найдено безопасных страниц для обхода: 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Вкладка: Главная</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:28</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Вкладка: Система</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:34</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Вкладка: Управление пользователями</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Вкладка: Интерфейсы</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:48</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Вкладка: SSH/HTTPS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:54</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Вкладка: 802.1X</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Вкладка: Настройка портов</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Вкладка: Состояние портов</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Вкладка: Информация об SFP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Вкладка: Зеркалирование портов</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Вкладка: 802.1Q</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:33</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Вкладка: Настройки</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:44</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Вкладка: Статус</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Вкладка: IGMP</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:58</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Вкладка: SMTP</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Вкладка: LLDP</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Вкладка: SNMP</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Вкладка: Входы/Выходы</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Вкладка: ИБП</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Вкладка: Авторестарт камер</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Вкладка: Пинг-запрос</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Вкладка: Статистика портов</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:41</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Вкладка: Графики</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:45</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Вкладка: ARP/MAC таблицы</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:52</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Вкладка: Журналы</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:56</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Вкладка: Syslog</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:19:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Вкладка: Настройки</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Без ошибок</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Страница отрисована корректно</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:19:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>web__navigation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Тест обхода меню (UI Errors)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Завершение</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Все доступные вкладки проверены</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -564,86 +2793,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:39</t>
+          <t>2026-05-05 16:16:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Сбор ссылок меню</t>
+          <t># Автотест начат</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Список собран</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Успех</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Найдено безопасных страниц для обхода: 27</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:46</t>
+          <t>2026-05-05 16:16:10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Вкладка: Главная</t>
+          <t># VLAN 1 — валидные имена</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Успех</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Страница отрисована корректно</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:50</t>
+          <t>2026-05-05 16:16:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Вкладка: Система</t>
+          <t>network vlan config vlanid 1 name test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -653,128 +2874,125 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Страница отрисована корректно</t>
+          <t>info: set vlan 1 name successfully!</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Вкладка: Управление пользователями</t>
+          <t>network vlan config vlanid 1 name test</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Ошибка</t>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сбой загрузки: Page.goto: Target page, context or browser has been closed
-Call log:
-  - navigating to "http://192.168.0.32/cgi-bin/luci/admin/system/acl", waiting until "networkidle"
-</t>
+          <t>info: set vlan 1 name successfully!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Вкладка: Интерфейсы</t>
+          <t>network vlan config vlanid 1 name testtesttest</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Ошибка</t>
+          <t>testtesttest</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>info: set vlan 1 name successfully!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Вкладка: SSH/HTTPS</t>
+          <t>network vlan config vlanid 1 name test12345</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Ошибка</t>
+          <t>test12345</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>info: set vlan 1 name successfully!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Вкладка: 802.1X</t>
+          <t>network vlan config vlanid 1 name тесттесттест</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>тесттесттест</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -784,29 +3002,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;тесттесттест&gt; not valid. russian symbol 'т' on position 1 is not allowed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Вкладка: Настройка портов</t>
+          <t>network vlan config vlanid 1 name тест12345</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>тест12345</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -816,61 +3034,61 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;тест12345&gt; not valid. russian symbol 'т' on position 1 is not allowed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Вкладка: Состояние портов</t>
+          <t>network vlan config vlanid 1 name 123456789</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Ошибка</t>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>info: set vlan 1 name successfully!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Вкладка: Информация об SFP</t>
+          <t>network vlan config vlanid 1 name a.b.c.d.e.f.g</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>a.b.c.d.e.f.g</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -880,93 +3098,89 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;a.b.c.d.e.f.g&gt; not valid. forbidden symbol '.' on position 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Вкладка: Зеркалирование портов</t>
+          <t>network vlan config vlanid 1 name TESTCAPSTESTCAPS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Ошибка</t>
+          <t>TESTCAPSTESTCAPS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>info: set vlan 1 name successfully!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Вкладка: 802.1Q</t>
+          <t># VLAN 1 — невалидные имена (ошибки ожидаемы)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Ошибка</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Вкладка: Настройки</t>
+          <t>network vlan config vlanid 1 name thisisaverylongstringmorethanthirtytwochars</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>thisisaverylongstringmorethanthirtytwochars</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -976,29 +3190,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name The value &lt;thisisaverylongstringmorethanthirtytwochars&gt; exceeds the maximum length: 32 symbols. This value has 43 symbols</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Вкладка: Статус</t>
+          <t>network vlan config vlanid 1 name строкасдлинойбольшетридцатидвухсимволоввней</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>строкасдлинойбольшетридцатидвухсимволоввней</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1008,29 +3222,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;строкасдлинойбольшетридцатидвухсимволоввней&gt; not valid. russian symbol 'с' on position 1 is not allowed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Вкладка: IGMP</t>
+          <t>network vlan config vlanid 1 name test!test</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test!test</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1040,29 +3254,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test\!test&gt; not valid. forbidden symbol '\' on position 5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Вкладка: SMTP</t>
+          <t>network vlan config vlanid 1 name test@test</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test@test</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1072,29 +3286,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test@test&gt; not valid. forbidden symbol '@' on position 5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Вкладка: LLDP</t>
+          <t>network vlan config vlanid 1 name test#test</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test#test</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1104,29 +3318,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test\#test&gt; not valid. forbidden symbol '\' on position 5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Вкладка: SNMP</t>
+          <t>network vlan config vlanid 1 name test$test</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test$test</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1136,29 +3350,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test$test&gt; not valid. forbidden symbol '$' on position 5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Вкладка: Входы/Выходы</t>
+          <t>network vlan config vlanid 1 name test%test</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test%test</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1168,29 +3382,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test%test&gt; not valid. forbidden symbol '%' on position 5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Вкладка: ИБП</t>
+          <t>network vlan config vlanid 1 name test^test</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test^test</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1200,29 +3414,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test^test&gt; not valid. forbidden symbol '^' on position 5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Вкладка: Авторестарт камер</t>
+          <t>network vlan config vlanid 1 name test&amp;test</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test&amp;test</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1232,29 +3446,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test\&amp;test&gt; not valid. forbidden symbol '\' on position 5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Вкладка: Пинг-запрос</t>
+          <t>network vlan config vlanid 1 name test*test</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test*test</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1264,29 +3478,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test*test&gt; not valid. forbidden symbol '*' on position 5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Вкладка: Статистика портов</t>
+          <t>network vlan config vlanid 1 name test=test</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test=test</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1296,29 +3510,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test=test&gt; not valid. forbidden symbol '=' on position 5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Вкладка: Графики</t>
+          <t>network vlan config vlanid 1 name test+test</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test+test</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1328,29 +3542,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test+test&gt; not valid. forbidden symbol '+' on position 5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Вкладка: ARP/MAC таблицы</t>
+          <t>network vlan config vlanid 1 name test(test</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test(test</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1360,29 +3574,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test\(test&gt; not valid. forbidden symbol '\' on position 5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Вкладка: Журналы</t>
+          <t>network vlan config vlanid 1 name test)test</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test)test</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1392,29 +3606,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test\)test&gt; not valid. forbidden symbol '\' on position 5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Вкладка: Syslog</t>
+          <t>network vlan config vlanid 1 name test[test</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test[test</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1424,29 +3638,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test[test&gt; not valid. forbidden symbol '[' on position 5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Вкладка: Настройки</t>
+          <t>network vlan config vlanid 1 name test]test</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Без ошибок</t>
+          <t>test]test</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1456,41 +3670,1243 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Сбой загрузки: Page.goto: Target page, context or browser has been closed</t>
+          <t>error: vlan name value &lt;test]test&gt; not valid. forbidden symbol ']' on position 5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:51</t>
+          <t>2026-05-05 16:16:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>web__navigation</t>
+          <t>ssh__UsIn__vlan__name__full</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Тест обхода меню (UI Errors)</t>
+          <t>network vlan config vlanid 1 name test{test</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Завершение</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+          <t>test{test</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;test{test&gt; not valid. forbidden symbol '{' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:56</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test}test</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>test}test</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;test}test&gt; not valid. forbidden symbol '}' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:58</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test;test</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>test;test</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;test\;test&gt; not valid. forbidden symbol '\' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:16:59</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test:test</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>test:test</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;test:test&gt; not valid. forbidden symbol ':' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test”test</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>test”test</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>info: set vlan 1 name successfully!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test'test</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>test'test</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;test'test&gt; not valid. forbidden symbol ''' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test\test</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>test\test</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>info: set vlan 1 name successfully!</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test|test</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>test|test</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;test\|test&gt; not valid. forbidden symbol '\' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name test/test</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>test/test</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;test/test&gt; not valid. forbidden symbol '/' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name question?</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>question?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>Выполнено</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Все доступные вкладки проверены</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name question
+    vlan name
+  &lt;cr&gt;  
+network vlan config vlanid 1 name question</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:09</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name data,comma</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>data,comma</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>info: set vlan 1 name successfully!
+network vlan config vlanid 1 name data,comma</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name tilde~wave</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>tilde~wave</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;data,comma&gt; not valid. forbidden symbol ',' on position 5
+network vlan config vlanid 1 name tilde~wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name angle&lt;test</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>angle&lt;test</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;tilde~wave&gt; not valid. forbidden symbol '~' on position 6
+network vlan config vlanid 1 name angle&lt;test</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name angle&gt;test</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>angle&gt;test</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;angle\&lt;test&gt; not valid. forbidden symbol '\' on position 6
+network vlan config vlanid 1 name angle&gt;test
+error: vlan name value &lt;angle\&gt;test&gt; not valid. forbidden symbol '\' on position 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:14</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name back`tick</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>back`tick</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>error: vlan name value &lt;back`tick&gt; not valid. forbidden symbol '`' on position 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name single’quote</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>single’quote</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>info: set vlan 1 name successfully!</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:18</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name line
+break</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>line
+break</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">network vlan config vlanid 1 name line
+info: set vlan 1 name successfully!
+break
+Syntax error: Unknown command
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name line
+break</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>line
+break</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">network vlan config vlanid 1 name line
+info: set vlan 1 name successfully!
+break
+Syntax error: Unknown command
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:21</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name tab	here</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>tab	here</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>network vlan config vlanid 1 name tabhere
+info: set vlan 1 name successfully!</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:22</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>changes revert</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Changes: 	
+	&gt;&gt; 	network	:
+		1	set		vlan1		descr		test		
+		2	set		vlan1		descr		testtesttest		
+		3	set		vlan1		descr		test12345		
+		4	set		vlan1		descr		123456789		
+		5	set		vlan1		descr		TESTCAPSTESTCAPS		
+		6	set		vlan1		descr		test”test		
+		7	set		vlan1		descr		testtest		
+		8	set		vlan1		descr		question		
+		9	set		vlan1		descr		single’quote		
+		10	set		vlan1		descr		line		
+		11	set		vlan1		descr		tabhere		
+	&gt;&gt; 	rpcd	:
+		1	add		login		
+		2	set		username		test_full		
+		3	set		password		$p$test_full		
+		4	set		hash		9161ee716951c03755f373ed984480be		
+		5	list-add		read		*		
+		6	list-add		write		*		
+		7	add		login		
+		8	set		username		test_user		
+		9	set		password		$p$test_user		
+		10	list-add		read		*		
+		11	add		login		
+		12	set		username		test_add_admin		
+		13	set		password		$p$test_add_admin		
+		14	list-add		read		*		
+		15	remove		
+		16	remove		
+info: configuration 	*	network	*	 was reverted
+info: configuration 	*	rpcd	*	 was reverted</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:22</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ssh__UsIn__vlan__name__full</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t># Автотест завершён</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ожидаемое значение</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t># Автотест начат</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>#1. Включение SNTP (Часовой пояс +3, Москва)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>services sntp config state enable</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>enable</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>info: operation state enable successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>services sntp config timezone 3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>info: operation timezone 3 successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>services sntp config add host_name www.ntp-servers.net</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>www.ntp-servers.net</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>info: operation add www.ntp-servers.net successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>changes save</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>info: new configuration saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>services sntp show configuration</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Синхр. UTC+3</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Рассинхрон! На коммутаторе: 05 May 2026 16:17:12, Ожидалось: 05 May 2026 14:17:31 (UTC+3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>#2. Возврат часового пояса на +5 (Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:32</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>services sntp config timezone 5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>info: operation timezone 5 successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:37</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>changes save</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>info: new configuration saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:39</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>services sntp show configuration</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Синхр. UTC+5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Время успешно синхронизировано (UTC+5): 05 May 2026 16:17:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:39</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>#3.Очистка (удаление тестового сервера)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:41</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>services sntp config delete host_name www.ntp-servers.net</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>www.ntp-servers.net</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Успех</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>info: operation delete www.ntp-servers.net successful!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:45</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>changes save</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>info: new configuration saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:17:45</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ssh__sntp__config</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t># Автотест завершён</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
